--- a/excel/Nectaro.xlsx
+++ b/excel/Nectaro.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Investavimas 2026.06.03\Nectaro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Investavimas 2026.06.03\Nectaro\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A74DAF38-3F8F-47F5-986B-A7BF5F154506}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BEF0DE-25CE-479D-A45E-7C474978D908}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -567,6 +567,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -587,9 +590,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1804,6 +1804,20 @@
     <dxf>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
           <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
@@ -1812,20 +1826,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -4531,43 +4531,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="28" t="s">
+      <c r="A1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="30"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="33" t="s">
+      <c r="J1" s="30"/>
+      <c r="K1" s="30"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="Q1" s="31" t="s">
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="Q1" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="R1" s="34"/>
-      <c r="S1" s="34"/>
-      <c r="T1" s="32"/>
-      <c r="U1" s="31" t="s">
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="33"/>
+      <c r="U1" s="32" t="s">
         <v>51</v>
       </c>
-      <c r="V1" s="32"/>
-      <c r="W1" s="28" t="s">
+      <c r="V1" s="33"/>
+      <c r="W1" s="29" t="s">
         <v>6</v>
       </c>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
       <c r="AA1" s="3" t="s">
         <v>56</v>
       </c>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="K3" s="19">
         <f ca="1">LVX0000P9SY1!B12</f>
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="L3" s="1" t="str">
         <f ca="1">LVX0000P9SY1!P3</f>
@@ -4755,7 +4755,7 @@
       </c>
       <c r="Z3" s="6">
         <f ca="1">XIRR(Pinigai!K2:K200,Pinigai!A2:A200)</f>
-        <v>0.1097764313220978</v>
+        <v>0.10804237723350527</v>
       </c>
       <c r="AA3" s="2">
         <f>SUM(O3:O100)</f>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="K4" s="19">
         <f ca="1">LVX0000PFLZ9!B12</f>
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="L4" s="1" t="str">
         <f ca="1">LVX0000PFLZ9!P3</f>
@@ -5531,7 +5531,7 @@
       </c>
       <c r="K15" s="19">
         <f ca="1">LVX0000QSAL3!B12</f>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L15" s="1" t="str">
         <f ca="1">LVX0000QSAL3!P3</f>
@@ -5661,7 +5661,7 @@
       </c>
       <c r="K17" s="19">
         <f ca="1">LVX0000R32A7!B12</f>
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="L17" s="1" t="str">
         <f ca="1">LVX0000R32A7!P3</f>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="K27" s="19">
         <f ca="1">LVX0000T2IU1!B12</f>
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="L27" s="1" t="str">
         <f ca="1">LVX0000T2IU1!P3</f>
@@ -6376,7 +6376,7 @@
       </c>
       <c r="K28" s="19">
         <f ca="1">LVX0000T2IT3!B12</f>
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="L28" s="1" t="str">
         <f ca="1">LVX0000T2IT3!P3</f>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="K29" s="19">
         <f ca="1">LVX0000ST8W0!B12</f>
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="L29" s="1" t="str">
         <f ca="1">LVX0000ST8W0!P3</f>
@@ -6506,7 +6506,7 @@
       </c>
       <c r="K30" s="19">
         <f ca="1">LVX0000TJMX6!B12</f>
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="L30" s="1" t="str">
         <f ca="1">LVX0000TJMX6!P3</f>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="K31" s="19">
         <f ca="1">LVX0000TL6K6!B12</f>
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="L31" s="1" t="str">
         <f ca="1">LVX0000TL6K6!P3</f>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="K32" s="19">
         <f ca="1">LVX0000TJR12!B12</f>
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L32" s="1" t="str">
         <f ca="1">LVX0000TJR12!P3</f>
@@ -6701,7 +6701,7 @@
       </c>
       <c r="K33" s="19">
         <f ca="1">LVX0000TJQV1!B12</f>
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="L33" s="1" t="str">
         <f ca="1">LVX0000TJQV1!P3</f>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="K34" s="19">
         <f ca="1">LVX0000TPE43!B12</f>
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="L34" s="1" t="str">
         <f ca="1">LVX0000TPE43!P3</f>
@@ -6831,7 +6831,7 @@
       </c>
       <c r="K35" s="19">
         <f ca="1">LVX0000TRIW9!B12</f>
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L35" s="1" t="str">
         <f ca="1">LVX0000TRIW9!P3</f>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="K36" s="19">
         <f ca="1">LVX0000TRJ61!B12</f>
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L36" s="1" t="str">
         <f ca="1">LVX0000TRJ61!P3</f>
@@ -6961,7 +6961,7 @@
       </c>
       <c r="K37" s="19">
         <f ca="1">LVX0000U4UG8!B12</f>
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="L37" s="1" t="str">
         <f ca="1">LVX0000U4UG8!P3</f>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="K38" s="19">
         <f ca="1">LVX0000ULW59!B12</f>
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="L38" s="1" t="str">
         <f ca="1">LVX0000ULW59!P3</f>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="K39" s="19">
         <f ca="1">LVX0000UP6R4!B12</f>
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="L39" s="1" t="str">
         <f ca="1">LVX0000UP6R4!P3</f>
@@ -7156,7 +7156,7 @@
       </c>
       <c r="K40" s="19">
         <f ca="1">LVX0000URIF2!B12</f>
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="L40" s="1" t="str">
         <f ca="1">LVX0000URIF2!P3</f>
@@ -7221,7 +7221,7 @@
       </c>
       <c r="K41" s="19">
         <f ca="1">'LVX0000URIF2 (2)'!B12</f>
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="L41" s="1" t="str">
         <f ca="1">'LVX0000URIF2 (2)'!P3</f>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="K42" s="19">
         <f ca="1">LVX0000UUJT5!B12</f>
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="L42" s="1" t="str">
         <f ca="1">LVX0000UUJT5!P3</f>
@@ -7351,7 +7351,7 @@
       </c>
       <c r="K43" s="19">
         <f ca="1">LVX0000UXVE6!B12</f>
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="L43" s="1" t="str">
         <f ca="1">LVX0000UXVE6!P3</f>
@@ -7416,7 +7416,7 @@
       </c>
       <c r="K44" s="19">
         <f ca="1">LVX0000UXVI7!B12</f>
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="L44" s="1" t="str">
         <f ca="1">LVX0000UXVI7!P3</f>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="K45" s="19">
         <f ca="1">LVX0000V3XU4!B12</f>
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="L45" s="1" t="str">
         <f ca="1">LVX0000V3XU4!P3</f>
@@ -7513,22 +7513,22 @@
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="Q1:T1"/>
   </mergeCells>
+  <conditionalFormatting sqref="A3:O45">
+    <cfRule type="expression" dxfId="175" priority="22">
+      <formula>$AC3="+"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="174" priority="23">
+      <formula>AND($M3&gt;0,$H3=$M3)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="AC3:AC45">
-    <cfRule type="expression" dxfId="175" priority="2">
+    <cfRule type="expression" dxfId="173" priority="2">
       <formula>AND($M3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC6:AC45">
-    <cfRule type="expression" dxfId="174" priority="1">
+    <cfRule type="expression" dxfId="172" priority="1">
       <formula>$AC6="+"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3:O45">
-    <cfRule type="expression" dxfId="173" priority="22">
-      <formula>$AC3="+"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="172" priority="23">
-      <formula>AND($M3&gt;0,$H3=$M3)</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
@@ -7608,29 +7608,29 @@
       <c r="B1" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -8893,29 +8893,29 @@
       <c r="B1" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -9253,7 +9253,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -10188,29 +10188,29 @@
       <c r="B1" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -11483,29 +11483,29 @@
       <c r="B1" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -12778,29 +12778,29 @@
       <c r="B1" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -14083,29 +14083,29 @@
       <c r="B1" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -14453,7 +14453,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -15388,29 +15388,29 @@
       <c r="B1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -15758,7 +15758,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -16693,29 +16693,29 @@
       <c r="B1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -17063,7 +17063,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -17998,29 +17998,29 @@
       <c r="B1" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -18368,7 +18368,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -19303,29 +19303,29 @@
       <c r="B1" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -19673,7 +19673,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -20591,7 +20591,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="28" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="10" t="s">
@@ -21017,7 +21017,7 @@
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A200" s="7">
         <f ca="1">TODAY()</f>
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="K200" s="24">
         <f>Overview!W3</f>
@@ -21056,29 +21056,29 @@
       <c r="B1" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -21426,7 +21426,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -22361,29 +22361,29 @@
       <c r="B1" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -22741,7 +22741,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -23679,29 +23679,29 @@
       <c r="B1" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -25007,29 +25007,29 @@
       <c r="B1" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -26342,29 +26342,29 @@
       <c r="B1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -27680,29 +27680,29 @@
       <c r="B1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -29008,29 +29008,29 @@
       <c r="B1" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -30359,29 +30359,29 @@
       <c r="B1" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -31687,29 +31687,29 @@
       <c r="B1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -33005,29 +33005,29 @@
       <c r="B1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -34320,29 +34320,29 @@
       <c r="B1" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -34662,7 +34662,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -35600,29 +35600,29 @@
       <c r="B1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -36925,29 +36925,29 @@
       <c r="B1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -37338,7 +37338,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -38276,29 +38276,29 @@
       <c r="B1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -39634,29 +39634,29 @@
       <c r="B1" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -40047,7 +40047,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -40980,29 +40980,29 @@
       <c r="B1" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -42313,29 +42313,29 @@
       <c r="B1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -43649,29 +43649,29 @@
       <c r="B1" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -44985,29 +44985,29 @@
       <c r="B1" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -46321,29 +46321,29 @@
       <c r="B1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -47637,29 +47637,29 @@
       <c r="B1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -48950,29 +48950,29 @@
       <c r="B1" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -49290,7 +49290,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -50228,29 +50228,29 @@
       <c r="B1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -51574,29 +51574,29 @@
       <c r="B1" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -52950,29 +52950,29 @@
       <c r="B1" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -54296,29 +54296,29 @@
       <c r="B1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -55659,29 +55659,29 @@
       <c r="B1" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -56092,7 +56092,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="D12" s="12">
         <v>46203</v>
@@ -57031,29 +57031,29 @@
       <c r="B1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -57464,7 +57464,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D12" s="12">
         <v>46203</v>
@@ -58403,29 +58403,29 @@
       <c r="B1" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -58743,7 +58743,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -59678,29 +59678,29 @@
       <c r="B1" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -60018,7 +60018,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -60953,29 +60953,29 @@
       <c r="B1" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -61293,7 +61293,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -62228,29 +62228,29 @@
       <c r="B1" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -62578,7 +62578,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
@@ -63513,29 +63513,29 @@
       <c r="B1" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="28" t="s">
-        <v>0</v>
-      </c>
-      <c r="H1" s="29"/>
-      <c r="I1" s="30"/>
+      <c r="E1" s="30"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="29" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="30"/>
+      <c r="I1" s="31"/>
       <c r="J1" s="18"/>
-      <c r="K1" s="28" t="s">
+      <c r="K1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="30"/>
-      <c r="X1" s="28"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="30"/>
+      <c r="L1" s="30"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="31"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="30"/>
+      <c r="Z1" s="31"/>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
@@ -63863,7 +63863,7 @@
       </c>
       <c r="B12" s="19">
         <f ca="1">IF(B16&lt;&gt;K3,(TODAY()-B11)*-1,"")</f>
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="D12" s="12"/>
       <c r="E12" s="12"/>
